--- a/artfynd/A 31037-2023 artfynd.xlsx
+++ b/artfynd/A 31037-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31037-2023 artfynd.xlsx
+++ b/artfynd/A 31037-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437578</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99413</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437580</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437581</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437535</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437568</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437539</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,6 +1558,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437541</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1625,6 +1670,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437537</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437570</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1839,6 +1894,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437571</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1946,6 +2006,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437573</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2053,6 +2118,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437575</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2160,6 +2230,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437576</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2267,6 +2342,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437586</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2374,6 +2454,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437588</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2481,6 +2566,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437589</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2588,6 +2678,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437560</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2695,6 +2790,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437562</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2802,6 +2902,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437563</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2909,6 +3014,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437565</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3016,6 +3126,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437566</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3123,6 +3238,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437524</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3230,6 +3350,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437525</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3337,6 +3462,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437526</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3444,6 +3574,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437527</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3551,6 +3686,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437528</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3658,6 +3798,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437529</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3765,6 +3910,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437530</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3872,6 +4022,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437531</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3979,6 +4134,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437532</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4086,6 +4246,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437583</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4193,6 +4358,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437585</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4307,6 +4477,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437536</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4414,6 +4589,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437543</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4521,6 +4701,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437544</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4628,6 +4813,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437546</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4735,6 +4925,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437549</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4842,6 +5037,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437550</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4949,6 +5149,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437552</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5056,6 +5261,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437554</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5163,6 +5373,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437555</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5270,6 +5485,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437557</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5377,6 +5597,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437559</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5484,6 +5709,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437533</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5591,8 +5821,61 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111437534</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>